--- a/docs/Logic Requirements/Ageipelago Barbarossa.xlsx
+++ b/docs/Logic Requirements/Ageipelago Barbarossa.xlsx
@@ -5,15 +5,21 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/BB6DD295C338E39F/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{0C991C93-049E-480B-942C-51325D210CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90237997-E5D0-487E-96E3-216EE2A48CB2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2A39F6-5AF4-4E2F-BEA0-D60F70B350FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EBDBD80-CAB1-4BA3-AD20-38FC2022F392}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{3EBDBD80-CAB1-4BA3-AD20-38FC2022F392}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Barbarossa" sheetId="1" r:id="rId1"/>
+    <sheet name="Holy Roman Emperor" sheetId="2" r:id="rId2"/>
+    <sheet name="Henry the Lion" sheetId="3" r:id="rId3"/>
+    <sheet name="Pope and Antipope" sheetId="4" r:id="rId4"/>
+    <sheet name="The Lombard League" sheetId="5" r:id="rId5"/>
+    <sheet name="Barbarossa's March" sheetId="6" r:id="rId6"/>
+    <sheet name="The Emperor Sleeping" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="200">
   <si>
     <t>Scenario</t>
   </si>
@@ -891,30 +897,6 @@
         <family val="2"/>
       </rPr>
       <t>Gallipoli</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>4 Transport Ships
-6 Transport Ships, 8 Galleons, 4 Fast Fire Ships, 3 Heavy Demolition Ships (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Constantinopel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
     </r>
   </si>
   <si>
@@ -2010,80 +1992,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-15 Chevalier
-12 Crossbowmen
-20 Elite Skirmishers
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-10 Chevalier
-7 Crossbowmen
-10 Elite Skirmishers
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Identical to Moderate</t>
-    </r>
-  </si>
-  <si>
     <t>The Player needs to have unlocked Monasteries and Monks and optained Villagers to gather the Relic.</t>
   </si>
   <si>
@@ -2275,84 +2183,6 @@
 12 Long Swordsmen
 10 Teutonic Knights
 2 Battering Rams
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Identical to Moderate</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-30 Champions
-15 Elite Throwing Axemen
-6 Bombard Cannons
-24 Galleons
-12 Demolition Ships
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-15 Champions
-5 Elite Throwing Axemen
-6 Bombard Cannons
-16 Galleons
-4 Demolition Ships
 </t>
     </r>
     <r>
@@ -3046,6 +2876,1029 @@
   <si>
     <r>
       <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Saracen Navy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is missing 1 Castle on Standard.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Seljuks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is missing 2 Castles of Standard.
+Defeating the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Saraven Navy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and destroying their Castle requires regular Troops and Warships from </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Constantinopel </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">and (except on Standard) Trebuchets.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Defeating </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Constantinopel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, destroying their Castle and reaching and destroying the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Wonder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> requires regular Troops and Trebuchets.
+Defeating </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF13E3F9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Gallipoli</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> requires only regular Troops.
+Reaching the shipwrecked Soldiers, the surrendering Cavalry Archers and the Hidden Monastery requires Warships from </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Constantinopel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> above Standard, on Standard any Ships.
+Defeating </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Seljuks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hospitallers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, destroying their Castles and reaching the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hospitallers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with any Troops requires Trebuchets and Warships from </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Constantinopel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> above Standard, on Standard any Ships</t>
+    </r>
+  </si>
+  <si>
+    <t>The Player needs to have unlocked Monasteries and Monks to gather the Relics.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+4 Monks
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+15 Halberdiers
+15 Elite Skirmishers
+4 Onagers
+7 Monks
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+6 Halberdiers
+6 Elite Skirmishers
+2 Onagers
+3 Monks
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Identical to Moderate</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+5 Elite War Elephants
+2 Onagers
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+20 Savar
+35 Elite War Elephants
+2 Onager
+4 Trebuchets
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+12 Savar
+10 Elite War Elephants
+2 Onagers
+4 Trebuchets
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+20 Savar
+35 Elite War Elephants
+8 Onagers
+4 Trebuchets</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+15 Elite Longbowmen
+4 Chevalier
+1 Trebuchet
+1 Richard the Lionheart
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+20 Elite Longbowmen
+14 Chevalier
+2 Onagers
+4 Trebuchets
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+25 Elite Longbowmen
+18 Chevalier
+5 Onagers
+4 Trebuchets
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+20 Elite Longbowmen
+14 Chevalier
+2 Onagers
+4 Trebuchets</t>
+    </r>
+  </si>
+  <si>
+    <t>Killable Units</t>
+  </si>
+  <si>
+    <t>Destructible Buildings</t>
+  </si>
+  <si>
+    <t>Deer</t>
+  </si>
+  <si>
+    <t>No items required</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>Sheep</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t>Wild Boar</t>
+  </si>
+  <si>
+    <t>Siege Workshop</t>
+  </si>
+  <si>
+    <t>Grey Wolf</t>
+  </si>
+  <si>
+    <t>Lumber Camp</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Town Center</t>
+  </si>
+  <si>
+    <t>Crossbowman</t>
+  </si>
+  <si>
+    <t>Stable</t>
+  </si>
+  <si>
+    <t>Scout Cavalry</t>
+  </si>
+  <si>
+    <t>Mill</t>
+  </si>
+  <si>
+    <t>Archery Range</t>
+  </si>
+  <si>
+    <t>Monk</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Monastery</t>
+  </si>
+  <si>
+    <t>Battering Ram</t>
+  </si>
+  <si>
+    <t>Mining Camp</t>
+  </si>
+  <si>
+    <t>Capped Ram</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>Barracks</t>
+  </si>
+  <si>
+    <t>Blacksmith</t>
+  </si>
+  <si>
+    <t>Castle</t>
+  </si>
+  <si>
+    <t>Light Cavalry</t>
+  </si>
+  <si>
+    <t>Stone Wall</t>
+  </si>
+  <si>
+    <t>Scorpion</t>
+  </si>
+  <si>
+    <t>Stone Gate</t>
+  </si>
+  <si>
+    <t>Fortified Wall</t>
+  </si>
+  <si>
+    <t>Trebuchet</t>
+  </si>
+  <si>
+    <t>Outpost</t>
+  </si>
+  <si>
+    <t>Watch Tower</t>
+  </si>
+  <si>
+    <t>Dock</t>
+  </si>
+  <si>
+    <t>Guard Tower</t>
+  </si>
+  <si>
+    <t>War Galley</t>
+  </si>
+  <si>
+    <t>Wonder</t>
+  </si>
+  <si>
+    <t>Galleon</t>
+  </si>
+  <si>
+    <t>Requires Transport Ship</t>
+  </si>
+  <si>
+    <t>Arbalester</t>
+  </si>
+  <si>
+    <t>Elite Skirmisher</t>
+  </si>
+  <si>
+    <t>Long Swordsman</t>
+  </si>
+  <si>
+    <t>Two-Handed Swordsman</t>
+  </si>
+  <si>
+    <t>Champion</t>
+  </si>
+  <si>
+    <t>Man-at-Arms</t>
+  </si>
+  <si>
+    <t>Knight</t>
+  </si>
+  <si>
+    <t>Mangonel</t>
+  </si>
+  <si>
+    <t>Spearman</t>
+  </si>
+  <si>
+    <t>Pikeman</t>
+  </si>
+  <si>
+    <t>Archer</t>
+  </si>
+  <si>
+    <t>Teutonic Knight</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+15 Cavalier
+12 Crossbowmen
+20 Elite Skirmishers
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+10 Cavalier
+7 Crossbowmen
+10 Elite Skirmishers
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Identical to Moderate</t>
+    </r>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Skirmisher</t>
+  </si>
+  <si>
+    <t>Trade Cart</t>
+  </si>
+  <si>
+    <t>Cavalry Archer</t>
+  </si>
+  <si>
+    <t>Elite Kipchak</t>
+  </si>
+  <si>
+    <t>Siege Onager</t>
+  </si>
+  <si>
+    <t>Manastery</t>
+  </si>
+  <si>
+    <t>Yurt</t>
+  </si>
+  <si>
+    <t>Yurt (Large)</t>
+  </si>
+  <si>
+    <t>Obuch</t>
+  </si>
+  <si>
+    <t>Fishing Ship</t>
+  </si>
+  <si>
+    <t>Transport Ship</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+30 Champions
+15 Elite Throwing Axemen
+6 Bombard Cannons
+24 Galleons
+12 Carracks
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+15 Champions
+5 Elite Throwing Axemen
+6 Bombard Cannons
+16 Galleons
+4 Carracks
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Identical to Moderate</t>
+    </r>
+  </si>
+  <si>
+    <t>War Hulk</t>
+  </si>
+  <si>
+    <t>Carrack</t>
+  </si>
+  <si>
+    <t>Throwing Axeman</t>
+  </si>
+  <si>
+    <t>Elite Throwing Axeman</t>
+  </si>
+  <si>
+    <t>Bombard Cannon</t>
+  </si>
+  <si>
+    <t>Hussar</t>
+  </si>
+  <si>
+    <t>Genoese Crossbowman</t>
+  </si>
+  <si>
+    <t>Hand Cannoneer</t>
+  </si>
+  <si>
+    <t>Elite Genoese Crossbowman</t>
+  </si>
+  <si>
+    <t>Trade Workshop</t>
+  </si>
+  <si>
+    <t>Cathedral</t>
+  </si>
+  <si>
+    <t>No items required
+Destroying the Cathedral is a Defeat Condition</t>
+  </si>
+  <si>
+    <t>Fire Ship</t>
+  </si>
+  <si>
+    <t>Requires Ships or Dock</t>
+  </si>
+  <si>
+    <t>Halberdier</t>
+  </si>
+  <si>
+    <t>Fast Fire Ship</t>
+  </si>
+  <si>
+    <t>Onager</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Battering Ram</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Only on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Paladin</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Scorpion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Only on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Pavilion</t>
+  </si>
+  <si>
+    <t>Pavilion (Large)</t>
+  </si>
+  <si>
+    <t>Bombard Tower</t>
+  </si>
+  <si>
+    <t>Fortified Gate</t>
+  </si>
+  <si>
+    <t>Archery Ramge</t>
+  </si>
+  <si>
+    <t>Elite Cataphract</t>
+  </si>
+  <si>
+    <t>Dire Wolf</t>
+  </si>
+  <si>
+    <t>Can convert to Player</t>
+  </si>
+  <si>
+    <t>Elite Mameluke</t>
+  </si>
+  <si>
+    <t>Heavy Camel Rider</t>
+  </si>
+  <si>
+    <r>
+      <t>4 Transport Ships
+6 Transport Ships, 4 Galleons, 4 Carracks, 4 Fast Fire Ships, 3 Heavy Demolition Ships (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Constantinopel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Heavy Demolition Ship</t>
+  </si>
+  <si>
+    <t>Requires Warships</t>
+  </si>
+  <si>
+    <t>Heavy Cavalry Archer</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <b/>
         <sz val="14"/>
         <color theme="1"/>
@@ -3066,14 +3919,14 @@
       <t xml:space="preserve">
 8 Heavy Camel Riders
 52 Heavy Cavalry Archers
-1 Onager
+4 Onager
 10 Bombard Cannons
 1 Trebuchet
 3 Monks
 Standard:
 8 Heavy Camel Riders
 47 Heavy Cavalry Archers
-4 Onagers
+1 Onagers
 10 Bombard Cannons
 1 Trebuchet
 3 Monks
@@ -3082,430 +3935,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Saracen Navy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is missing 1 Castle on Standard.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Seljuks</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is missing 2 Castles of Standard.
-Defeating the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Saraven Navy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and destroying their Castle requires regular Troops and Warships from </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Constantinopel </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">and (except on Standard) Trebuchets.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Defeating </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Constantinopel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, destroying their Castle and reaching and destroying the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Wonder</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> requires regular Troops and Trebuchets.
-Defeating </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF13E3F9"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gallipoli</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> requires only regular Troops.
-Reaching the shipwrecked Soldiers, the surrendering Cavalry Archers and the Hidden Monastery requires Warships from </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Constantinopel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> above Standard, on Standard any Ships.
-Defeating </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Seljuks</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> or </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hospitallers</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, destroying their Castles and reaching the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hospitallers</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> with any Troops requires Trebuchets and Warships from </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Constantinopel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> above Standard, on Standard any Ships</t>
-    </r>
-  </si>
-  <si>
-    <t>The Player needs to have unlocked Monasteries and Monks to gather the Relics.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-4 Monks
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-15 Halberdiers
-15 Elite Skirmishers
-4 Onagers
-7 Monks
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-6 Halberdiers
-6 Elite Skirmishers
-2 Onagers
-3 Monks
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Identical to Moderate</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-5 Elite War Elephants
-2 Onagers
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-20 Savar
-35 Elite War Elephants
-2 Onager
-4 Trebuchets
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-12 Savar
-10 Elite War Elephants
-2 Onagers
-4 Trebuchets
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-20 Savar
-35 Elite War Elephants
-8 Onagers
-4 Trebuchets</t>
-    </r>
+    <t>Frankish Paladin</t>
   </si>
   <si>
     <r>
@@ -3531,20 +3961,43 @@
 4 Heavy Camel Riders
 8 Elite Mamelucks
 2 Siege Onagers
-19 Galleons
+11 Galleons
+12 Carracks
 8 Fire Ships
-8 Heavy Demolition Ships
+4 Heavy Demolition Ships
 1 Elite Cannon Galleon
 Standard:
 4 Heavy Camel Riders
 8 Elite Mamelukes
 2 Siege Onagers
-12 Galleons
-5 Fire Ships
-5 Heavy Demolition Ships
+7 Galleons
+8 Carracks
+4 Fire Ships
+3 Heavy Demolition Ships
 Hard:
 Identical to Moderate</t>
     </r>
+  </si>
+  <si>
+    <t>Sea Wall</t>
+  </si>
+  <si>
+    <t>Sea Gate</t>
+  </si>
+  <si>
+    <t>Fish Trap</t>
+  </si>
+  <si>
+    <t>Keep</t>
+  </si>
+  <si>
+    <t>Elite War Elephant</t>
+  </si>
+  <si>
+    <t>Savar</t>
+  </si>
+  <si>
+    <t>Archer of the Eyes</t>
   </si>
   <si>
     <r>
@@ -3554,7 +4007,7 @@
 12 Elite Mamelukes
 4 Siege Onagers
 3 Trebuchets
-2 Archers of the Eye
+5 Archers of the Eye
 </t>
     </r>
     <r>
@@ -3643,90 +4096,40 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-15 Elite Longbowmen
-4 Chevalier
-1 Trebuchet
-1 Richard the Lionheart
-</t>
-    </r>
+    <t>Mameluke</t>
+  </si>
+  <si>
+    <t>Elite Longbowman</t>
+  </si>
+  <si>
+    <t>Light Cavaly</t>
+  </si>
+  <si>
+    <t>Richard the Lionheart</t>
+  </si>
+  <si>
+    <t>Dome of the Rock</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-20 Elite Longbowmen
-14 Chevalier
-2 Onagers
-4 Trebuchets
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-25 Elite Longbowmen
-18 Chevalier
-5 Onagers
-4 Trebuchets
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-20 Elite Longbowmen
-14 Chevalier
-2 Onagers
-4 Trebuchets</t>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Heavy Scorpion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
     </r>
   </si>
 </sst>
@@ -3734,7 +4137,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3760,12 +4163,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FF3A3A3A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
@@ -3820,13 +4217,6 @@
     <font>
       <sz val="14"/>
       <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FF3A3A3A"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3903,6 +4293,73 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF13E3F9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3912,7 +4369,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -4000,11 +4457,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4018,28 +4523,125 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4409,282 +5011,2928 @@
         <v>7</v>
       </c>
       <c r="J3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" s="4" t="s">
+    </row>
+    <row r="4" spans="2:17" ht="225.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="244.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="4" spans="2:17" ht="225.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="2:17" ht="244.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="J5" s="8" t="s">
+      <c r="G6" s="9"/>
+      <c r="H6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="10" t="s">
+    </row>
+    <row r="7" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="8" t="s">
+      <c r="F8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="N8" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="K7" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="10" t="s">
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="J8" s="8" t="s">
+      <c r="G9" s="9"/>
+      <c r="H9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="K8" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="L8" s="8" t="s">
+      <c r="K9" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="L9" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8EBFBFB-BFC3-45F2-8AE9-505265B14120}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K20" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K21" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K22" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K23" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="L23" s="18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+    </row>
+    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+    </row>
+    <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G26" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+    </row>
+    <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G27" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="K36" s="27"/>
+      <c r="L36" s="27"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D60ED6AB-7469-4698-A695-2E8BCBEAD83F}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="K15" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="K16" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="K17" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="L17" s="18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="K36" s="27"/>
+      <c r="L36" s="27"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AF93BD0-8221-4F04-B861-3D32DC9024E1}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K17" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K18" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K19" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K22" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K24" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="L24" s="18" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+    </row>
+    <row r="30" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G30" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+    </row>
+    <row r="34" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G34" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="K36" s="27"/>
+      <c r="L36" s="27"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3796EF8C-0DF4-42C0-8E88-79C463DF95B7}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G12" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G13" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G14" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G15" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G16" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K18" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K19" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K20" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K21" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="L22" s="18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K23" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+    </row>
+    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+    </row>
+    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G29" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+    </row>
+    <row r="30" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G30" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="H30" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="K36" s="27"/>
+      <c r="L36" s="27"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C99364C-16DE-4EA8-AD87-2D8BFC5C34F4}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G3" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G5" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G6" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G11" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G12" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G21" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G22" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="K22" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G23" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="K23" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="K24" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="K25" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G26" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="K26" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G27" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="K27" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G28" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K28" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="L28" s="18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="K36" s="27"/>
+      <c r="L36" s="27"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E99AFAD-4CB3-492B-BAFB-AA98FB2D25D5}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K4" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K17" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="K26" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="L26" s="18" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="K36" s="27"/>
+      <c r="L36" s="27"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>